--- a/artfynd/A 28820-2025 artfynd.xlsx
+++ b/artfynd/A 28820-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>156208</v>
       </c>
       <c r="B2" t="n">
-        <v>83131</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>383751.4934040805</v>
+        <v>383751</v>
       </c>
       <c r="R2" t="n">
-        <v>6286357.911387885</v>
+        <v>6286358</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -757,19 +752,9 @@
           <t>2012-09-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-09-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,15 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1053983</v>
+        <v>199848</v>
       </c>
       <c r="B3" t="n">
-        <v>83136</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,46 +798,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3518</v>
+        <v>535</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Brid.) E.Britton</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björkelund, O om gården, Hl</t>
+          <t>Björkelund, öster om gården, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>383751.4934040805</v>
+        <v>383672</v>
       </c>
       <c r="R3" t="n">
-        <v>6286357.911387885</v>
+        <v>6286357</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,22 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-09-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-02-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-09-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-02-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +876,14 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kulturgranskog</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr"/>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>tallstubbe</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -929,15 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>82670476</v>
+        <v>717176</v>
       </c>
       <c r="B4" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,40 +910,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3884</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björkelund, Hl</t>
+          <t>Björkelund, i O, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>383718.7664670212</v>
+        <v>383889</v>
       </c>
       <c r="R4" t="n">
-        <v>6286308.842834743</v>
+        <v>6286559</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,22 +964,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-03-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2003-05-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-03-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2003-05-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,22 +978,579 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Jord</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Kjell Georgson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kjell Georgson, Ebba Werner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>107295051</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Björkelund, Skottelundsbacken, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>383812</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6286289</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Breared</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-10-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-10-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>lövskog</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>stenmur</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>Jan-Erik Hederås</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>JEH-9295</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jan-Erik Hederås</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jan-Erik Hederås, Gunilla Hederås, Kjell Georgson, Ebba Werner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1053983</v>
+      </c>
+      <c r="B6" t="n">
+        <v>85274</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3518</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Smal svampklubba</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tolypocladium ophioglossoides</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björkelund, O om gården, Hl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>383751</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6286358</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Breared</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2012-09-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2012-09-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Kulturgranskog</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kjell Georgson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kjell Georgson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>82670476</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92497</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björkelund, Hl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>383719</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6286309</v>
+      </c>
+      <c r="S7" t="n">
+        <v>75</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Breared</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-03-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-03-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Moa Pettersson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Moa Pettersson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>83865471</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Björkelund, Hl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>383791</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6286323</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Breared</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-03-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-03-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>111224599</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Björkelund, Hl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>383745</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6286231</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Breared</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-04-30</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-04-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28820-2025 artfynd.xlsx
+++ b/artfynd/A 28820-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/156208</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/199848</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/717176</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107295051</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1053983</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1333,6 +1363,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82670476</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1444,6 +1479,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83865471</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1551,8 +1591,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111224599</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>